--- a/VerveStacks_CAN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8CE918-6B89-4868-8113-CF46D05C740D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1BC659-E141-433A-B39E-00EA2E2AD1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15251,7 +15251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6549C1B-A8E6-4BD9-B104-33F9D2CAFCD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CBEEDA1-6D90-411D-BC60-2F63EEE5CAF1}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1BC659-E141-433A-B39E-00EA2E2AD1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF97A878-C6DC-43FB-91A5-C9CA78750EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15251,7 +15251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CBEEDA1-6D90-411D-BC60-2F63EEE5CAF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342B349B-1115-4C7E-BD2C-F5BFB215867C}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF97A878-C6DC-43FB-91A5-C9CA78750EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2D42D7-C139-4903-B21D-1E8C7A2C0D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15251,7 +15251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342B349B-1115-4C7E-BD2C-F5BFB215867C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AF6D95-780D-4C03-B9AD-C2E3E006B1B8}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
